--- a/output/第10期計画_見える化入力マニュアルの点検と整合確認.xlsx
+++ b/output/第10期計画_見える化入力マニュアルの点検と整合確認.xlsx
@@ -902,12 +902,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>当方未算定</t>
+          <t>令和8年9月24日に算定済み</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>当方は補正後被保険者数を係数で一括算定。段階別の将来人数は出していない</t>
+          <t>令和6年度の実績の構成比を固定し、将来の第1号被保険者数に乗じて16段階×8年度を算定した（確認事項No.156）</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -915,9 +915,9 @@
           <t>04・07</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>受託者で可</t>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>解消</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>当方未算定</t>
+          <t>令和8年9月24日に算定済み</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>当方の見込量は令和9〜11・17・22年度の5年度。人口の基礎は令和32年度まであるため算定は広げられる</t>
+          <t>中長期の年次を5年次へ広げた（確認事項No.157）。地域密着型介護老人福祉施設が定員を超えるのは令和17年度ではなく令和12年度であることが分かった</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -945,9 +945,9 @@
           <t>05</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>受託者で可</t>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>解消</t>
         </is>
       </c>
     </row>
@@ -1993,17 +1993,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>テンプレートが求める年度のうち当方が未算定のものを数えられること</t>
+          <t>テンプレートが求める年度をすべて算定したこと</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>8年度 − 5年度</t>
+          <t>8年度 − 当方の算定</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>R12／R27／R32（99項目）</t>
+          <t>未算定 0年度（令和8年9月24日に令和12・27・32年度を算定）</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数が当方未算定</t>
+          <t>所得段階別第1号被保険者数（令和8年9月24日に算定した）</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>令和6・7年度の段階別の実績の構成比で按分すれば出せる。補正後被保険者数と整合させる。受託者の作業だけで進む。</t>
+          <t>令和8年9月24日に算定した（確認事項No.156）。令和6年度の実績の構成比を固定し将来の第1号被保険者数に乗じている。構成比を令和6年度に採ったのは当方が採用している係数と同じにするためで、令和7年度に改めると月額が163円下がる（係数の選択そのもの）。当連合は16段階であるため入力は「弾力化」となる。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -3743,9 +3743,9 @@
           <t>No.156</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>解消</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>令和12・27・32年度が当方未算定</t>
+          <t>令和12・27・32年度（令和8年9月24日に算定した）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>人口の基礎（案C・社人研の伸び）は令和32年度まであるため、見込量の算定を3年度分広げれば埋まる。受託者の作業だけで進む。</t>
+          <t>令和8年9月24日に中長期を5年次へ広げた（確認事項No.157）。あわせて、地域密着型介護老人福祉施設が定員を超えるのは令和17年度ではなく令和12年度であることが分かった。計画本文に掲げるのは従前どおり令和17年度・令和22年度である。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -3773,9 +3773,9 @@
           <t>No.157</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>解消</t>
         </is>
       </c>
     </row>
@@ -4238,20 +4238,20 @@
         <v>260</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="E12" s="15" t="n">
         <v>6</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>影響額32件・市町村特別給付8件・拠出率6件・償還金6件・相互財政安定化12件は確認のうえ0、収納率6件は99.0％、給付費の上乗せ40件は按分すれば出せる（計110件）。準備基金残高6件は未受領。所得段階別112件（No.156）・準備基金取崩額6件・交付金の交付見込額6件（No.86）・調整交付金の調整5件はご判断・未算定。地域支援事業費8件は自動計算、結果確認7件は確認操作。</t>
+          <t>令和8年9月24日に所得段階別112件を算定した（確認事項No.156）。影響額32件・市町村特別給付8件・拠出率6件・償還金6件・相互財政安定化12件は確認のうえ0、収納率6件は99.0％、給付費の上乗せ40件は按分すれば出せる（計222件）。準備基金残高6件は未受領。準備基金取崩額6件・交付金の交付見込額6件（No.86）・調整交付金の調整5件はご判断。地域支援事業費8件は自動計算、結果確認7件は確認操作。</t>
         </is>
       </c>
     </row>
@@ -4296,13 +4296,13 @@
         <v>615</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>151</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>187</v>
@@ -4474,9 +4474,9 @@
       <c r="C8" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>未算定</t>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>算定済み</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -4484,11 +4484,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>人口は案C（令和11年度まで）に社人研の伸びで接続して出せる。見込量の算定を広げれば埋まる</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -4550,9 +4546,9 @@
       <c r="C11" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>未算定</t>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>算定済み</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -4560,11 +4556,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>人口は案C（令和11年度まで）に社人研の伸びで接続して出せる。見込量の算定を広げれば埋まる</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="6" t="n">
@@ -4578,9 +4570,9 @@
       <c r="C12" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>未算定</t>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>算定済み</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -4588,11 +4580,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>人口は案C（令和11年度まで）に社人研の伸びで接続して出せる。見込量の算定を広げれば埋まる</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="11" t="inlineStr"/>
@@ -4602,13 +4590,9 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>R12／R27／R32</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
       <c r="E13" s="11" t="inlineStr"/>
       <c r="F13" s="11" t="inlineStr">
         <is>

--- a/output/第10期計画_見える化入力マニュアルの点検と整合確認.xlsx
+++ b/output/第10期計画_見える化入力マニュアルの点検と整合確認.xlsx
@@ -580,7 +580,7 @@
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>【評価の結論】
-様式としての作りは妥当です。手順が見える化システムの画面順（0〜8）と一致し、①入力シート→②町用転記票→③登録確認の連動（数式参照・COUNTIFS・所得段階の合計照合）が働いています。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額6,436円を小数第4位まで再現します（08シート・自己点検6）。
+様式としての作りは妥当です。手順が見える化システムの画面順（0〜8）と一致し、①入力シート→②町用転記票→③登録確認の連動（数式参照・COUNTIFS・所得段階の合計照合）が働いています。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現します（08シート・自己点検6）。
 そのまま本件に用いるには手当てを要します。全国共通版であり広域連合を想定していません（09シート）。また当方の算定と作りが違う箇所が4つあります（人口系列・交付金の控除・給付費の上乗せ項目・低所得者軽減公費）。いずれも03シートに掲げました。</t>
         </is>
       </c>
@@ -697,7 +697,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>J÷K＝6436.0914円。当方の算定上の月額6436.0914円と差0.0001円未満</t>
+          <t>J÷K＝6438.2557円。当方の算定上の月額6438.2557円と差0.0001円未満</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>6436.0914円 対 6436.0914円（差0.000000円）</t>
+          <t>6438.2557円 対 6438.2557円（差0.000000円）</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>6436.09円（当方 6436.09円）</t>
+          <t>6438.26円（当方 6438.26円）</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>別のものであることを説明に明記する。当方の算定上の月額は6436円であり、百円未満四捨五入して6,400円である。</t>
+          <t>別のものであることを説明に明記する。当方の算定上の月額は6438円であり、百円未満四捨五入して6,400円である。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>729,213,412円（3か年計）</t>
+          <t>729,464,444円（3か年計）</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>算定上6436円（基準額6,400円）</t>
+          <t>算定上6438円（基準額6,400円）</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>9,565,616,321</t>
+          <t>9,569,019,924</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>10,097,100,098</t>
+          <t>10,100,503,701</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>9,887,004,275</t>
+          <t>9,890,407,878</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>2,322,333,022</t>
+          <t>2,323,115,851</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>494,350,214</t>
+          <t>494,520,394</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>729,213,412</t>
+          <t>729,464,444</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>2,087,469,824</t>
+          <t>2,088,171,801</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>6436.09円</t>
+          <t>6438.26円</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824円</t>
+          <t>2,088,171,801円</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>6436.0914円</t>
+          <t>6438.2557円</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>6436.0914円</t>
+          <t>6438.2557円</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>11,705,811円</t>
+          <t>12,407,788円</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>36.09円</t>
+          <t>38.26円</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>6436.09円</t>
+          <t>6438.26円</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
